--- a/Analysed/GPT/Analysis_Summary_Depth_without_vernier_gpt5.4Thinking.xlsx
+++ b/Analysed/GPT/Analysis_Summary_Depth_without_vernier_gpt5.4Thinking.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.6374 ± 2.7027</t>
+          <t>3.0766 ± 1.6058</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.5473 ± 3.3093</t>
+          <t>3.9059 ± 2.0365</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.3500 ± 0.0599</t>
+          <t>0.4204 ± 0.1633</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,38 +521,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="C2" t="n">
-        <v>1.72625</v>
+        <v>2.187651515151515</v>
       </c>
       <c r="D2" t="n">
-        <v>2.207296989532673</v>
+        <v>2.851763542622407</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3924050632911392</v>
+        <v>0.7251908396946565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.405869852438506</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2560975609756098</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.041724137931034</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.4567528553287</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.355294117647059</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.626578268250593</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.72625</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.207296989532673</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3924050632911392</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>53</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C7" t="n">
         <v>5.548490566037736</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D7" t="n">
         <v>6.887354148714246</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E7" t="n">
         <v>0.3076923076923077</v>
       </c>
     </row>
